--- a/output/pdf_financials_xlsx/TAO.xlsx
+++ b/output/pdf_financials_xlsx/TAO.xlsx
@@ -1087,22 +1087,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.158559</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06715500000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.386892</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.748824</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1.069185</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.773859</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2049,22 +2049,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-18.874565</v>
+        <v>-18.716006</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.600542</v>
+        <v>-2.533387</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.090142</v>
+        <v>-0.70325</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>12.376019</v>
+        <v>13.124843</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.073359</v>
+        <v>6.142544</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14.731055</v>
+        <v>15.504914</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-69.762517</v>
@@ -2169,22 +2169,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-18.874565</v>
+        <v>-18.716006</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.600542</v>
+        <v>-2.533387</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.090142</v>
+        <v>-0.70325</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>12.376019</v>
+        <v>13.124843</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.073359</v>
+        <v>6.142544</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14.731055</v>
+        <v>15.504914</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-69.762517</v>
@@ -2229,19 +2229,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-403.7771954219702</v>
+        <v>-400.3851962776768</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-83.50988245864795</v>
+        <v>-81.35336810259813</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-16.68654249516421</v>
+        <v>-10.76447931528574</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>45.34161092458569</v>
+        <v>48.08505261282097</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16.60638209494538</v>
+        <v>20.10609395057874</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -70107,7 +70107,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E618" s="5" t="n">

--- a/output/pdf_financials_xlsx/TAO.xlsx
+++ b/output/pdf_financials_xlsx/TAO.xlsx
@@ -779,34 +779,34 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.007218</v>
+        <v>1.239051</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.363582</v>
+        <v>1.751666</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.080439</v>
+        <v>2.377356</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2.366092</v>
+        <v>2.749592</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.778248</v>
+        <v>2.696778</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.628893</v>
+        <v>2.540696</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.696767</v>
+        <v>2.814437</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.601843</v>
+        <v>2.338297</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.631487</v>
+        <v>2.501269</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.903861</v>
+        <v>1.780488</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>23.485322</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.572102</v>
+        <v>2.955602</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>23.956331</v>
@@ -1417,10 +1417,10 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.639197</v>
+        <v>-0.639197</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.001655</v>
+        <v>-0.001655</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -1649,7 +1649,7 @@
         <v>7.682708</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-69.762517</v>
+        <v>-68.384434</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-79.438908</v>
@@ -1709,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-1.378083</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-5.165898</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.00415</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.193897</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -33581,7 +33581,11 @@
           <t>Private placement 7</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -58353,7 +58357,11 @@
           <t>Purchase of shares</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E498" s="5" t="n">
         <v>-0.00415</v>
       </c>
@@ -64227,7 +64235,11 @@
           <t>Consulting and director fees</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -65806,7 +65818,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
           <t>-</t>
@@ -66497,7 +66513,11 @@
           <t>Consulting and directors fees</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr">
         <is>
           <t>-</t>
@@ -67586,7 +67606,11 @@
           <t>Consulting and directors’ fees</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
@@ -68790,7 +68814,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D605" t="inlineStr"/>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E605" t="inlineStr">
         <is>
           <t>-</t>
@@ -68889,7 +68917,11 @@
           <t>Net loss from discontinued operations (Note 14(a))</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E606" t="inlineStr">
         <is>
           <t>-</t>
@@ -70402,7 +70434,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E621" t="inlineStr">
         <is>
           <t>-</t>
@@ -73388,7 +73424,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E651" t="inlineStr">
         <is>
           <t>-</t>
@@ -74287,7 +74327,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E660" t="inlineStr">
         <is>
           <t>-</t>
